--- a/光伏配储项目/电价数据/2026/和平站.xlsx
+++ b/光伏配储项目/电价数据/2026/和平站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.4821</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7555700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.53996</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.55523</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48329</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47416</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12822</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.12727</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.03116</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20632</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.03204</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.02651</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.14765</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13703</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.07673999999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.04312</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.50986</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53744</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73407</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12297</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19706</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6613600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19642</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41311</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27584</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98652</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28214</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.47798</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43671</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6831900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7333999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08356</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95445</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.89335</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76146</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42764</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71745</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8899199999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94314</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50288</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5253099999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50969</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50983</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.16307</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.02348</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.08365</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49308</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50406</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.11256</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12279</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.0481</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.01421</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02364</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.03193</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78261</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.25649</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.13889</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.21427</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.23956</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.54232</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5928099999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74337</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7543800000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16157</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.25003</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13063</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83766</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20536</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10626</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02215</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09049</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65151</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98339</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9142400000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95763</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77952</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88597</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7357</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.78095</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7263500000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.75949</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49337</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.03756</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78032</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.46163</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5062099999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28549</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64624</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5464199999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48334</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6177699999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.56923</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.71612</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60101</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.51763</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50327</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.07998000000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12243</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.03827000000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.24913</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17369</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15765</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11976</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62437</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47492</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5098</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48541</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54863</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49508</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4694700000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32138</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.08868999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07484</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15606</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09393000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.08526</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.15831</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.15766</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.03822</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.01402</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.00433</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01876</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42269</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48747</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54898</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37275</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.86907</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46454</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.53696</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.62414</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10214</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19673</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15112</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04905</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34811</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32384</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86922</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57766</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5429700000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45932</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.67248</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50707</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62976</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.8198200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8844299999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.67177</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05688</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.81212</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87522</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51952</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9150900000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.54516</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48756</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44731</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37281</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9370299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5321900000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47865</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.47051</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6197999999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.21906</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08757</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47981</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46605</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7932400000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9506699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48441</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20467</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7316</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82357</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68272</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.81517</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.6046699999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47757</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52864</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44144</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48146</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.62037</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48824</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45832</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51852</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44606</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52658</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42195</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63475</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5724400000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01732</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25918</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.65707</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55987</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5263600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5141100000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37238</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.52388</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41394</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.52238</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.56464</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5363600000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.5027900000000001</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21417</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09754</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11493</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08198</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.08968000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26523</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25636</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12576</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02709</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05454999999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16039</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07325</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42893</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45861</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54989</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47077</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.46073</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.53499</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53746</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41163</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39272</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6871</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5722200000000001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49885</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48702</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44624</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54811</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17267</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.10663</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21374</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19392</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.15539</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.16922</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.17029</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.11987</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.16416</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.15568</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.13636</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.52738</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39633</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.63942</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.64676</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43917</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.13543</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6796</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51806</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46476</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25947</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.18775</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25573</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55452</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.13071</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58208</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46759</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72094</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.06815</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.9082</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.73278</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5293300000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6819299999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42862</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.48089</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.47263</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.60638</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.09115</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.52651</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5502</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37542</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23363</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12441</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21984</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15293</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21628</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.4756</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.57043</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6816599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63922</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6578200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84945</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6262300000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.2106</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.67855</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61048</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39088</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.59537</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73342</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6369400000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.91452</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48273</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45774</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47242</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46564</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.48076</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.46133</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45871</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.49114</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.44022</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48815</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46436</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.48052</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5629500000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.55057</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62871</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54364</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6175900000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53965</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46865</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.47336</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64746</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6146200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.26869</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43215</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47438</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.64213</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64452</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.71145</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9594600000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.1897</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.30741</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.94297</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.11426</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.92792</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.70314</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.15789</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78908</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.64264</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69198</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.59557</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59237</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.58036</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.57204</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.70111</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.54726</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44401</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43573</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.58065</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.62806</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.46141</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26333</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>-0.03116</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.51803</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02243</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.52588</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46908</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49692</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.5238400000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46892</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4785</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47443</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.51478</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.53267</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.46989</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.62952</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.48187</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49617</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.50245</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48563</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.4724100000000001</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.63289</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.60182</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59581</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44337</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.57056</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45892</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43619</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45927</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55515</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.55333</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.57011</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49849</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.20773</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21004</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43696</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22873</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07177</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.08674999999999999</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10594</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18093</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22192</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27387</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21348</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.5016700000000001</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.4938</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50897</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46783</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42835</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52291</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51609</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.52739</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.5182899999999999</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.51576</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.5196900000000001</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.5126000000000001</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03421</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15166</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01488</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02949</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03716</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01491</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03557</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54308</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.4119</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.19864</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.02792</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49627</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.88778</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52954</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.54408</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.59939</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.51386</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4751</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48826</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.48263</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.64601</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44282</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.66871</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.57872</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.66043</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.60414</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.66185</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.6297</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.61139</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.63659</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46636</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.5432899999999999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.60221</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.52691</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.42284</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9118999999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87354</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.03861</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.03588</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.04875</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00498</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.05267</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16565</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.12287</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00115</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.15123</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.05369</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15813</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8636699999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8619199999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86605</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96287</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.15388</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.15411</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.14792</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.42388</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60881</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.90124</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.49167</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.8464400000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51966</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.6284099999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.53588</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6718099999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46374</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.6297999999999999</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.54223</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.50954</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6204500000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6781200000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5003500000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52776</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.23272</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.21341</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45184</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.6343099999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.25854</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5102099999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.49154</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.68131</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.4051</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49997</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48686</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.48103</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5521900000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.86593</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.01944</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8462799999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.7852100000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6041599999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.01738</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83262</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46661</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5844</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55786</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.66016</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.57582</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.9299299999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.81492</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6157999999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.61861</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.54512</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5428999999999999</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40418</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.53195</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44437</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.71169</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7888200000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5482400000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.78235</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48509</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6203500000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.95196</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5484600000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.53139</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.02219</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.44031</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40846</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.62262</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17744</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17448</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09865</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18523</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01477</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05692</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11109</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02693</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00219</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18337</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20841</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.52151</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47521</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.48213</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.42062</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.26847</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26704</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.10153</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41098</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38986</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48463</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17691</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02288</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24214</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03407</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03448</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.02462</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.03321</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03817</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00851</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.05311</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.08663</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11734</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.14208</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.13697</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02185</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.10123</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14795</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26425</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4317</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.4091</v>
       </c>
     </row>
   </sheetData>
